--- a/universal-file-converter/apps/desktop/src-tauri/tests/fixtures/sample.xlsx
+++ b/universal-file-converter/apps/desktop/src-tauri/tests/fixtures/sample.xlsx
@@ -1,8 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>